--- a/docs/Requerimiento apk nuevo.xlsx
+++ b/docs/Requerimiento apk nuevo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\santi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\personal\async\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E93946-73DC-4F1C-97D6-6A88FBD82616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A46DDC-7DD1-401B-86AF-7BB39E6D5D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{0A6DF2EB-2459-43CE-97E1-242861658C4F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="1" activeTab="6" xr2:uid="{0A6DF2EB-2459-43CE-97E1-242861658C4F}"/>
   </bookViews>
   <sheets>
     <sheet name="Requerimiento nuevo APK" sheetId="1" r:id="rId1"/>
@@ -23,10 +23,21 @@
     <sheet name="Tabla Registro de preguntas" sheetId="8" r:id="rId8"/>
     <sheet name="Criterio registro de preguntas" sheetId="7" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1463,7 +1474,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1490,52 +1501,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1545,18 +1521,42 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2555,9 +2555,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2595,7 +2595,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2701,7 +2701,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2843,7 +2843,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2852,27 +2852,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0765A19A-CC1F-4DDF-ACFA-91FCB39213CA}">
   <dimension ref="A3:L16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="9" max="9" width="25.44140625" customWidth="1"/>
-    <col min="10" max="10" width="42.109375" customWidth="1"/>
-    <col min="11" max="11" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.88671875" customWidth="1"/>
+    <col min="9" max="9" width="25.453125" customWidth="1"/>
+    <col min="10" max="10" width="42.08984375" customWidth="1"/>
+    <col min="11" max="11" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-    </row>
-    <row r="4" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+    </row>
+    <row r="4" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
       <c r="I4" s="1" t="s">
         <v>1</v>
       </c>
@@ -2880,17 +2880,17 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
       <c r="I6" s="2" t="s">
         <v>2</v>
       </c>
@@ -2898,11 +2898,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
+    <row r="7" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
       <c r="I7" s="5" t="s">
         <v>4</v>
       </c>
@@ -2910,11 +2910,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="87" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
+    <row r="8" spans="1:12" ht="87" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="23"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
       <c r="I8" s="5" t="s">
         <v>6</v>
       </c>
@@ -2922,13 +2922,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="23"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="I11" s="7" t="s">
         <v>69</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="I12" s="11" t="s">
         <v>72</v>
       </c>
@@ -2952,11 +2952,11 @@
       <c r="K12" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="L12" s="13" t="s">
+      <c r="L12" s="24" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="I13" s="11" t="s">
         <v>76</v>
       </c>
@@ -2966,9 +2966,9 @@
       <c r="K13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="L13" s="13"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L13" s="24"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="I14" s="11" t="s">
         <v>78</v>
       </c>
@@ -2978,9 +2978,9 @@
       <c r="K14" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="L14" s="13"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L14" s="24"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="I15" s="11" t="s">
         <v>80</v>
       </c>
@@ -2990,9 +2990,9 @@
       <c r="K15" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="L15" s="13"/>
-    </row>
-    <row r="16" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L15" s="24"/>
+    </row>
+    <row r="16" spans="1:12" ht="43.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="I16" s="6" t="s">
         <v>82</v>
       </c>
@@ -3002,7 +3002,7 @@
       <c r="K16" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="L16" s="13"/>
+      <c r="L16" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3026,19 +3026,19 @@
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="E3:H23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="5" max="5" width="26.88671875" customWidth="1"/>
-    <col min="6" max="6" width="48.21875" customWidth="1"/>
-    <col min="7" max="8" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.90625" customWidth="1"/>
+    <col min="6" max="6" width="48.1796875" customWidth="1"/>
+    <col min="7" max="8" width="32.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E3" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="17" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="5:8" x14ac:dyDescent="0.35">
       <c r="E17" s="10" t="s">
         <v>252</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="18" spans="5:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="5:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E18" s="3" t="s">
         <v>253</v>
       </c>
@@ -3066,7 +3066,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="19" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="5:8" x14ac:dyDescent="0.35">
       <c r="E19" s="3" t="s">
         <v>255</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="20" spans="5:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="5:8" ht="28.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E20" s="3" t="s">
         <v>256</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="21" spans="5:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="5:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E21" s="3" t="s">
         <v>257</v>
       </c>
@@ -3108,7 +3108,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="22" spans="5:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="5:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E22" s="3" t="s">
         <v>260</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="23" spans="5:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="5:8" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E23" s="3" t="s">
         <v>262</v>
       </c>
@@ -3148,87 +3148,87 @@
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="G1:AG32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="10" max="10" width="2.77734375" style="29" customWidth="1"/>
-    <col min="20" max="20" width="3.44140625" style="29" customWidth="1"/>
-    <col min="29" max="29" width="3.44140625" style="38" customWidth="1"/>
+    <col min="10" max="10" width="2.81640625" style="18" customWidth="1"/>
+    <col min="20" max="20" width="3.453125" style="18" customWidth="1"/>
+    <col min="29" max="29" width="3.453125" style="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:33" x14ac:dyDescent="0.3">
-      <c r="U1" s="31" t="s">
+    <row r="1" spans="7:33" x14ac:dyDescent="0.35">
+      <c r="U1" s="26" t="s">
         <v>350</v>
       </c>
-      <c r="V1" s="16"/>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16"/>
-      <c r="Z1" s="39" t="s">
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Z1" s="28" t="s">
         <v>379</v>
       </c>
-      <c r="AA1" s="39"/>
-      <c r="AB1" s="39"/>
-      <c r="AD1" s="31" t="s">
+      <c r="AA1" s="28"/>
+      <c r="AB1" s="28"/>
+      <c r="AD1" s="26" t="s">
         <v>378</v>
       </c>
-      <c r="AE1" s="16"/>
-      <c r="AF1" s="16"/>
-      <c r="AG1" s="16"/>
-    </row>
-    <row r="2" spans="7:33" x14ac:dyDescent="0.3">
-      <c r="G2" s="30" t="s">
+      <c r="AE1" s="27"/>
+      <c r="AF1" s="27"/>
+      <c r="AG1" s="27"/>
+    </row>
+    <row r="2" spans="7:33" x14ac:dyDescent="0.35">
+      <c r="G2" s="31" t="s">
         <v>347</v>
       </c>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="Q2" s="23" t="s">
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="Q2" s="29" t="s">
         <v>347</v>
       </c>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Z2" s="39"/>
-      <c r="AA2" s="39"/>
-      <c r="AB2" s="39"/>
-      <c r="AD2" s="16"/>
-      <c r="AE2" s="16"/>
-      <c r="AF2" s="16"/>
-      <c r="AG2" s="16"/>
-    </row>
-    <row r="3" spans="7:33" x14ac:dyDescent="0.3">
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="Q3" s="23"/>
-      <c r="R3" s="23"/>
-      <c r="S3" s="23"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="39"/>
-      <c r="AB3" s="39"/>
-    </row>
-    <row r="4" spans="7:33" x14ac:dyDescent="0.3">
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
-      <c r="S4" s="23"/>
-      <c r="U4" s="37" t="s">
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="27"/>
+      <c r="Z2" s="28"/>
+      <c r="AA2" s="28"/>
+      <c r="AB2" s="28"/>
+      <c r="AD2" s="27"/>
+      <c r="AE2" s="27"/>
+      <c r="AF2" s="27"/>
+      <c r="AG2" s="27"/>
+    </row>
+    <row r="3" spans="7:33" x14ac:dyDescent="0.35">
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
+      <c r="S3" s="29"/>
+      <c r="Z3" s="28"/>
+      <c r="AA3" s="28"/>
+      <c r="AB3" s="28"/>
+    </row>
+    <row r="4" spans="7:33" x14ac:dyDescent="0.35">
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="U4" s="25" t="s">
         <v>351</v>
       </c>
-      <c r="V4" s="37"/>
-      <c r="W4" s="37"/>
-      <c r="X4" s="37"/>
-      <c r="AD4" s="37" t="s">
+      <c r="V4" s="25"/>
+      <c r="W4" s="25"/>
+      <c r="X4" s="25"/>
+      <c r="AD4" s="25" t="s">
         <v>351</v>
       </c>
-      <c r="AE4" s="37"/>
-      <c r="AF4" s="37"/>
-      <c r="AG4" s="37"/>
-    </row>
-    <row r="6" spans="7:33" x14ac:dyDescent="0.3">
+      <c r="AE4" s="25"/>
+      <c r="AF4" s="25"/>
+      <c r="AG4" s="25"/>
+    </row>
+    <row r="6" spans="7:33" x14ac:dyDescent="0.35">
       <c r="U6" t="s">
         <v>293</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="7" spans="7:33" x14ac:dyDescent="0.3">
+    <row r="7" spans="7:33" x14ac:dyDescent="0.35">
       <c r="U7" t="s">
         <v>294</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="8" spans="7:33" x14ac:dyDescent="0.3">
+    <row r="8" spans="7:33" x14ac:dyDescent="0.35">
       <c r="U8" t="s">
         <v>295</v>
       </c>
@@ -3283,11 +3283,11 @@
       <c r="W8" t="s">
         <v>354</v>
       </c>
-      <c r="Z8" s="23" t="s">
+      <c r="Z8" s="29" t="s">
         <v>355</v>
       </c>
-      <c r="AA8" s="23"/>
-      <c r="AB8" s="23"/>
+      <c r="AA8" s="29"/>
+      <c r="AB8" s="29"/>
       <c r="AD8" t="s">
         <v>295</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="9" spans="7:33" x14ac:dyDescent="0.3">
+    <row r="9" spans="7:33" x14ac:dyDescent="0.35">
       <c r="U9" t="s">
         <v>296</v>
       </c>
@@ -3310,9 +3310,9 @@
       <c r="W9" t="s">
         <v>354</v>
       </c>
-      <c r="Z9" s="23"/>
-      <c r="AA9" s="23"/>
-      <c r="AB9" s="23"/>
+      <c r="Z9" s="29"/>
+      <c r="AA9" s="29"/>
+      <c r="AB9" s="29"/>
       <c r="AD9" t="s">
         <v>296</v>
       </c>
@@ -3324,7 +3324,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="10" spans="7:33" x14ac:dyDescent="0.3">
+    <row r="10" spans="7:33" x14ac:dyDescent="0.35">
       <c r="U10" t="s">
         <v>297</v>
       </c>
@@ -3335,9 +3335,9 @@
       <c r="W10" t="s">
         <v>354</v>
       </c>
-      <c r="Z10" s="23"/>
-      <c r="AA10" s="23"/>
-      <c r="AB10" s="23"/>
+      <c r="Z10" s="29"/>
+      <c r="AA10" s="29"/>
+      <c r="AB10" s="29"/>
       <c r="AD10" t="s">
         <v>297</v>
       </c>
@@ -3349,12 +3349,12 @@
         <v>354</v>
       </c>
     </row>
-    <row r="11" spans="7:33" x14ac:dyDescent="0.3">
-      <c r="Q11" s="23" t="s">
+    <row r="11" spans="7:33" x14ac:dyDescent="0.35">
+      <c r="Q11" s="29" t="s">
         <v>348</v>
       </c>
-      <c r="R11" s="23"/>
-      <c r="S11" s="23"/>
+      <c r="R11" s="29"/>
+      <c r="S11" s="29"/>
       <c r="U11" t="s">
         <v>306</v>
       </c>
@@ -3365,9 +3365,9 @@
       <c r="W11" t="s">
         <v>354</v>
       </c>
-      <c r="Z11" s="23"/>
-      <c r="AA11" s="23"/>
-      <c r="AB11" s="23"/>
+      <c r="Z11" s="29"/>
+      <c r="AA11" s="29"/>
+      <c r="AB11" s="29"/>
       <c r="AD11" t="s">
         <v>306</v>
       </c>
@@ -3379,15 +3379,15 @@
         <v>354</v>
       </c>
     </row>
-    <row r="12" spans="7:33" x14ac:dyDescent="0.3">
-      <c r="G12" s="23" t="s">
+    <row r="12" spans="7:33" x14ac:dyDescent="0.35">
+      <c r="G12" s="29" t="s">
         <v>348</v>
       </c>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
-      <c r="S12" s="23"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="Q12" s="29"/>
+      <c r="R12" s="29"/>
+      <c r="S12" s="29"/>
       <c r="U12" t="s">
         <v>307</v>
       </c>
@@ -3409,13 +3409,13 @@
         <v>354</v>
       </c>
     </row>
-    <row r="13" spans="7:33" x14ac:dyDescent="0.3">
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
+    <row r="13" spans="7:33" x14ac:dyDescent="0.35">
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="Q13" s="29"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
       <c r="U13" t="s">
         <v>312</v>
       </c>
@@ -3437,26 +3437,26 @@
         <v>354</v>
       </c>
     </row>
-    <row r="14" spans="7:33" x14ac:dyDescent="0.3">
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-    </row>
-    <row r="15" spans="7:33" x14ac:dyDescent="0.3">
-      <c r="U15" s="37" t="s">
+    <row r="14" spans="7:33" x14ac:dyDescent="0.35">
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+    </row>
+    <row r="15" spans="7:33" x14ac:dyDescent="0.35">
+      <c r="U15" s="25" t="s">
         <v>356</v>
       </c>
-      <c r="V15" s="37"/>
-      <c r="W15" s="37"/>
-      <c r="X15" s="37"/>
-      <c r="AD15" s="37" t="s">
+      <c r="V15" s="25"/>
+      <c r="W15" s="25"/>
+      <c r="X15" s="25"/>
+      <c r="AD15" s="25" t="s">
         <v>356</v>
       </c>
-      <c r="AE15" s="37"/>
-      <c r="AF15" s="37"/>
-      <c r="AG15" s="37"/>
-    </row>
-    <row r="16" spans="7:33" x14ac:dyDescent="0.3">
+      <c r="AE15" s="25"/>
+      <c r="AF15" s="25"/>
+      <c r="AG15" s="25"/>
+    </row>
+    <row r="16" spans="7:33" x14ac:dyDescent="0.35">
       <c r="V16" t="s">
         <v>369</v>
       </c>
@@ -3464,7 +3464,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="17" spans="7:33" x14ac:dyDescent="0.3">
+    <row r="17" spans="7:33" x14ac:dyDescent="0.35">
       <c r="U17" t="s">
         <v>357</v>
       </c>
@@ -3478,12 +3478,12 @@
         <v>368</v>
       </c>
     </row>
-    <row r="18" spans="7:33" x14ac:dyDescent="0.3">
-      <c r="Q18" s="14" t="s">
+    <row r="18" spans="7:33" x14ac:dyDescent="0.35">
+      <c r="Q18" s="30" t="s">
         <v>349</v>
       </c>
-      <c r="R18" s="14"/>
-      <c r="S18" s="14"/>
+      <c r="R18" s="30"/>
+      <c r="S18" s="30"/>
       <c r="U18" t="s">
         <v>358</v>
       </c>
@@ -3497,15 +3497,15 @@
         <v>368</v>
       </c>
     </row>
-    <row r="19" spans="7:33" x14ac:dyDescent="0.3">
-      <c r="G19" s="14" t="s">
+    <row r="19" spans="7:33" x14ac:dyDescent="0.35">
+      <c r="G19" s="30" t="s">
         <v>346</v>
       </c>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="Q19" s="14"/>
-      <c r="R19" s="14"/>
-      <c r="S19" s="14"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="Q19" s="30"/>
+      <c r="R19" s="30"/>
+      <c r="S19" s="30"/>
       <c r="U19" t="s">
         <v>359</v>
       </c>
@@ -3519,24 +3519,24 @@
         <v>368</v>
       </c>
     </row>
-    <row r="20" spans="7:33" x14ac:dyDescent="0.3">
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14"/>
+    <row r="20" spans="7:33" x14ac:dyDescent="0.35">
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
       <c r="U20" t="s">
         <v>360</v>
       </c>
       <c r="V20" t="s">
         <v>368</v>
       </c>
-      <c r="Z20" s="23" t="s">
+      <c r="Z20" s="29" t="s">
         <v>370</v>
       </c>
-      <c r="AA20" s="23"/>
-      <c r="AB20" s="23"/>
+      <c r="AA20" s="29"/>
+      <c r="AB20" s="29"/>
       <c r="AD20" t="s">
         <v>360</v>
       </c>
@@ -3544,22 +3544,22 @@
         <v>368</v>
       </c>
     </row>
-    <row r="21" spans="7:33" x14ac:dyDescent="0.3">
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="Q21" s="14"/>
-      <c r="R21" s="14"/>
-      <c r="S21" s="14"/>
+    <row r="21" spans="7:33" x14ac:dyDescent="0.35">
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="Q21" s="30"/>
+      <c r="R21" s="30"/>
+      <c r="S21" s="30"/>
       <c r="U21" t="s">
         <v>361</v>
       </c>
       <c r="V21" t="s">
         <v>368</v>
       </c>
-      <c r="Z21" s="23"/>
-      <c r="AA21" s="23"/>
-      <c r="AB21" s="23"/>
+      <c r="Z21" s="29"/>
+      <c r="AA21" s="29"/>
+      <c r="AB21" s="29"/>
       <c r="AD21" t="s">
         <v>361</v>
       </c>
@@ -3567,22 +3567,22 @@
         <v>368</v>
       </c>
     </row>
-    <row r="22" spans="7:33" x14ac:dyDescent="0.3">
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="Q22" s="14"/>
-      <c r="R22" s="14"/>
-      <c r="S22" s="14"/>
+    <row r="22" spans="7:33" x14ac:dyDescent="0.35">
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="Q22" s="30"/>
+      <c r="R22" s="30"/>
+      <c r="S22" s="30"/>
       <c r="U22" t="s">
         <v>362</v>
       </c>
       <c r="V22" t="s">
         <v>368</v>
       </c>
-      <c r="Z22" s="23"/>
-      <c r="AA22" s="23"/>
-      <c r="AB22" s="23"/>
+      <c r="Z22" s="29"/>
+      <c r="AA22" s="29"/>
+      <c r="AB22" s="29"/>
       <c r="AD22" t="s">
         <v>362</v>
       </c>
@@ -3590,22 +3590,22 @@
         <v>368</v>
       </c>
     </row>
-    <row r="23" spans="7:33" x14ac:dyDescent="0.3">
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="Q23" s="14"/>
-      <c r="R23" s="14"/>
-      <c r="S23" s="14"/>
+    <row r="23" spans="7:33" x14ac:dyDescent="0.35">
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
       <c r="U23" t="s">
         <v>363</v>
       </c>
       <c r="V23" t="s">
         <v>368</v>
       </c>
-      <c r="Z23" s="23"/>
-      <c r="AA23" s="23"/>
-      <c r="AB23" s="23"/>
+      <c r="Z23" s="29"/>
+      <c r="AA23" s="29"/>
+      <c r="AB23" s="29"/>
       <c r="AD23" t="s">
         <v>363</v>
       </c>
@@ -3613,13 +3613,13 @@
         <v>368</v>
       </c>
     </row>
-    <row r="24" spans="7:33" x14ac:dyDescent="0.3">
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="14"/>
+    <row r="24" spans="7:33" x14ac:dyDescent="0.35">
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="Q24" s="30"/>
+      <c r="R24" s="30"/>
+      <c r="S24" s="30"/>
       <c r="U24" t="s">
         <v>364</v>
       </c>
@@ -3633,13 +3633,13 @@
         <v>368</v>
       </c>
     </row>
-    <row r="25" spans="7:33" x14ac:dyDescent="0.3">
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="Q25" s="14"/>
-      <c r="R25" s="14"/>
-      <c r="S25" s="14"/>
+    <row r="25" spans="7:33" x14ac:dyDescent="0.35">
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="Q25" s="30"/>
+      <c r="R25" s="30"/>
+      <c r="S25" s="30"/>
       <c r="U25" t="s">
         <v>365</v>
       </c>
@@ -3653,10 +3653,10 @@
         <v>368</v>
       </c>
     </row>
-    <row r="26" spans="7:33" x14ac:dyDescent="0.3">
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
+    <row r="26" spans="7:33" x14ac:dyDescent="0.35">
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
       <c r="U26" t="s">
         <v>366</v>
       </c>
@@ -3670,7 +3670,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="27" spans="7:33" x14ac:dyDescent="0.3">
+    <row r="27" spans="7:33" x14ac:dyDescent="0.35">
       <c r="U27" t="s">
         <v>367</v>
       </c>
@@ -3684,21 +3684,21 @@
         <v>368</v>
       </c>
     </row>
-    <row r="29" spans="7:33" x14ac:dyDescent="0.3">
-      <c r="U29" s="37" t="s">
+    <row r="29" spans="7:33" x14ac:dyDescent="0.35">
+      <c r="U29" s="25" t="s">
         <v>371</v>
       </c>
-      <c r="V29" s="37"/>
-      <c r="W29" s="37"/>
-      <c r="X29" s="37"/>
-      <c r="AD29" s="37" t="s">
+      <c r="V29" s="25"/>
+      <c r="W29" s="25"/>
+      <c r="X29" s="25"/>
+      <c r="AD29" s="25" t="s">
         <v>371</v>
       </c>
-      <c r="AE29" s="37"/>
-      <c r="AF29" s="37"/>
-      <c r="AG29" s="37"/>
-    </row>
-    <row r="30" spans="7:33" x14ac:dyDescent="0.3">
+      <c r="AE29" s="25"/>
+      <c r="AF29" s="25"/>
+      <c r="AG29" s="25"/>
+    </row>
+    <row r="30" spans="7:33" x14ac:dyDescent="0.35">
       <c r="U30" t="s">
         <v>372</v>
       </c>
@@ -3712,7 +3712,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="31" spans="7:33" x14ac:dyDescent="0.3">
+    <row r="31" spans="7:33" x14ac:dyDescent="0.35">
       <c r="U31" t="s">
         <v>373</v>
       </c>
@@ -3726,7 +3726,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="32" spans="7:33" x14ac:dyDescent="0.3">
+    <row r="32" spans="7:33" x14ac:dyDescent="0.35">
       <c r="U32" t="s">
         <v>374</v>
       </c>
@@ -3742,6 +3742,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="G19:I26"/>
+    <mergeCell ref="G2:I4"/>
+    <mergeCell ref="G12:I14"/>
+    <mergeCell ref="Q2:S4"/>
+    <mergeCell ref="Q11:S13"/>
+    <mergeCell ref="Q18:S25"/>
     <mergeCell ref="U29:X29"/>
     <mergeCell ref="AD1:AG2"/>
     <mergeCell ref="AD4:AG4"/>
@@ -3753,12 +3759,6 @@
     <mergeCell ref="Z8:AB11"/>
     <mergeCell ref="U15:X15"/>
     <mergeCell ref="Z20:AB23"/>
-    <mergeCell ref="G19:I26"/>
-    <mergeCell ref="G2:I4"/>
-    <mergeCell ref="G12:I14"/>
-    <mergeCell ref="Q2:S4"/>
-    <mergeCell ref="Q11:S13"/>
-    <mergeCell ref="Q18:S25"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
@@ -3775,23 +3775,23 @@
     <tabColor theme="5" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="F6:G9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="6" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F6" s="23" t="s">
+    <row r="6" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F6" s="29" t="s">
         <v>381</v>
       </c>
-      <c r="G6" s="23"/>
-    </row>
-    <row r="7" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-    </row>
-    <row r="8" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-    </row>
-    <row r="9" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="G6" s="29"/>
+    </row>
+    <row r="7" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+    </row>
+    <row r="8" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+    </row>
+    <row r="9" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
     </row>
@@ -3810,18 +3810,18 @@
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.44140625" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" customWidth="1"/>
+    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>382</v>
       </c>
@@ -3829,142 +3829,142 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>65</v>
       </c>
@@ -3980,13 +3980,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{658D155B-8ED2-4D1E-BD09-4B7116899CF7}">
   <dimension ref="A1:H29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" customWidth="1"/>
-    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="1" max="1" width="18.453125" customWidth="1"/>
+    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -3997,7 +3998,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -4005,81 +4006,81 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>20</v>
       </c>
       <c r="B7" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>22</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -4087,7 +4088,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -4095,7 +4096,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -4103,7 +4104,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -4111,7 +4112,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -4119,7 +4120,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -4127,7 +4128,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -4135,7 +4136,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -4143,7 +4144,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -4151,7 +4152,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -4159,7 +4160,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -4167,7 +4168,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -4175,7 +4176,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -4183,7 +4184,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -4191,7 +4192,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -4199,7 +4200,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -4207,7 +4208,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -4215,7 +4216,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -4223,7 +4224,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -4231,7 +4232,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>62</v>
       </c>
@@ -4239,7 +4240,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>64</v>
       </c>
@@ -4261,15 +4262,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68C2EAE2-A4DD-4364-B421-A60A077D726C}">
   <dimension ref="A1:D166"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" customWidth="1"/>
-    <col min="2" max="2" width="16.21875" customWidth="1"/>
-    <col min="3" max="3" width="23.77734375" customWidth="1"/>
-    <col min="4" max="4" width="21.5546875" customWidth="1"/>
+    <col min="1" max="1" width="18.453125" customWidth="1"/>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.81640625" customWidth="1"/>
+    <col min="4" max="4" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -4283,7 +4284,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -4297,7 +4298,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -4311,7 +4312,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -4325,7 +4326,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -4339,7 +4340,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -4353,7 +4354,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -4367,7 +4368,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -4381,7 +4382,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -4395,7 +4396,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -4409,7 +4410,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -4423,7 +4424,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -4437,7 +4438,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -4451,7 +4452,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -4465,7 +4466,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -4479,7 +4480,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -4493,7 +4494,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -4507,7 +4508,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -4521,7 +4522,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -4535,7 +4536,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -4549,7 +4550,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -4563,7 +4564,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -4577,7 +4578,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -4591,7 +4592,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -4605,7 +4606,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>16</v>
       </c>
@@ -4619,7 +4620,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -4633,7 +4634,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -4647,7 +4648,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -4661,7 +4662,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -4675,7 +4676,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -4689,7 +4690,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -4703,7 +4704,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -4717,7 +4718,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>20</v>
       </c>
@@ -4731,7 +4732,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>20</v>
       </c>
@@ -4745,7 +4746,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>20</v>
       </c>
@@ -4759,7 +4760,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>20</v>
       </c>
@@ -4773,7 +4774,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>20</v>
       </c>
@@ -4787,7 +4788,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>20</v>
       </c>
@@ -4801,7 +4802,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>20</v>
       </c>
@@ -4815,7 +4816,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>22</v>
       </c>
@@ -4829,7 +4830,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>22</v>
       </c>
@@ -4843,7 +4844,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>22</v>
       </c>
@@ -4857,7 +4858,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>22</v>
       </c>
@@ -4871,7 +4872,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>22</v>
       </c>
@@ -4885,7 +4886,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>22</v>
       </c>
@@ -4899,7 +4900,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -4913,7 +4914,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>22</v>
       </c>
@@ -4927,7 +4928,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>22</v>
       </c>
@@ -4941,7 +4942,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>24</v>
       </c>
@@ -4955,7 +4956,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>24</v>
       </c>
@@ -4969,7 +4970,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>24</v>
       </c>
@@ -4983,7 +4984,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>26</v>
       </c>
@@ -4997,7 +4998,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>26</v>
       </c>
@@ -5011,7 +5012,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>26</v>
       </c>
@@ -5025,7 +5026,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>26</v>
       </c>
@@ -5039,7 +5040,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>26</v>
       </c>
@@ -5053,7 +5054,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>26</v>
       </c>
@@ -5067,7 +5068,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>26</v>
       </c>
@@ -5081,7 +5082,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>26</v>
       </c>
@@ -5095,7 +5096,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>26</v>
       </c>
@@ -5109,7 +5110,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>26</v>
       </c>
@@ -5123,7 +5124,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>28</v>
       </c>
@@ -5137,7 +5138,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>28</v>
       </c>
@@ -5151,7 +5152,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>28</v>
       </c>
@@ -5165,7 +5166,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>28</v>
       </c>
@@ -5179,7 +5180,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -5193,7 +5194,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>28</v>
       </c>
@@ -5207,7 +5208,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>30</v>
       </c>
@@ -5221,7 +5222,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>30</v>
       </c>
@@ -5235,7 +5236,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>30</v>
       </c>
@@ -5249,7 +5250,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>30</v>
       </c>
@@ -5263,7 +5264,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>30</v>
       </c>
@@ -5277,7 +5278,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>30</v>
       </c>
@@ -5291,7 +5292,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>30</v>
       </c>
@@ -5305,7 +5306,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>30</v>
       </c>
@@ -5319,7 +5320,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>32</v>
       </c>
@@ -5333,7 +5334,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>32</v>
       </c>
@@ -5347,7 +5348,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>32</v>
       </c>
@@ -5361,7 +5362,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>32</v>
       </c>
@@ -5375,7 +5376,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>32</v>
       </c>
@@ -5389,7 +5390,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>32</v>
       </c>
@@ -5403,7 +5404,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>32</v>
       </c>
@@ -5417,7 +5418,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>34</v>
       </c>
@@ -5431,7 +5432,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>34</v>
       </c>
@@ -5445,7 +5446,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>34</v>
       </c>
@@ -5459,7 +5460,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>34</v>
       </c>
@@ -5473,7 +5474,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>34</v>
       </c>
@@ -5487,7 +5488,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>34</v>
       </c>
@@ -5501,7 +5502,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>34</v>
       </c>
@@ -5515,7 +5516,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>36</v>
       </c>
@@ -5529,7 +5530,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>36</v>
       </c>
@@ -5543,7 +5544,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>36</v>
       </c>
@@ -5557,7 +5558,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>36</v>
       </c>
@@ -5571,7 +5572,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>36</v>
       </c>
@@ -5585,7 +5586,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>36</v>
       </c>
@@ -5599,7 +5600,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>38</v>
       </c>
@@ -5613,7 +5614,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>38</v>
       </c>
@@ -5627,7 +5628,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>38</v>
       </c>
@@ -5641,7 +5642,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>38</v>
       </c>
@@ -5655,7 +5656,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>38</v>
       </c>
@@ -5669,7 +5670,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>40</v>
       </c>
@@ -5683,7 +5684,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>40</v>
       </c>
@@ -5697,7 +5698,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>40</v>
       </c>
@@ -5711,7 +5712,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>40</v>
       </c>
@@ -5725,7 +5726,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>40</v>
       </c>
@@ -5739,7 +5740,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>40</v>
       </c>
@@ -5753,7 +5754,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>40</v>
       </c>
@@ -5767,7 +5768,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>42</v>
       </c>
@@ -5781,7 +5782,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>42</v>
       </c>
@@ -5795,7 +5796,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>42</v>
       </c>
@@ -5809,7 +5810,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>42</v>
       </c>
@@ -5823,7 +5824,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>44</v>
       </c>
@@ -5837,7 +5838,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>44</v>
       </c>
@@ -5851,7 +5852,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>44</v>
       </c>
@@ -5865,7 +5866,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>44</v>
       </c>
@@ -5879,7 +5880,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>44</v>
       </c>
@@ -5893,7 +5894,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>46</v>
       </c>
@@ -5907,7 +5908,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>46</v>
       </c>
@@ -5921,7 +5922,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>48</v>
       </c>
@@ -5935,7 +5936,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>48</v>
       </c>
@@ -5949,7 +5950,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>50</v>
       </c>
@@ -5963,7 +5964,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>50</v>
       </c>
@@ -5977,7 +5978,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>50</v>
       </c>
@@ -5991,7 +5992,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>50</v>
       </c>
@@ -6005,7 +6006,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>50</v>
       </c>
@@ -6019,7 +6020,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>52</v>
       </c>
@@ -6033,7 +6034,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>52</v>
       </c>
@@ -6047,7 +6048,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>52</v>
       </c>
@@ -6061,7 +6062,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>52</v>
       </c>
@@ -6075,7 +6076,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>52</v>
       </c>
@@ -6089,7 +6090,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>52</v>
       </c>
@@ -6103,7 +6104,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>52</v>
       </c>
@@ -6117,7 +6118,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>52</v>
       </c>
@@ -6131,7 +6132,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>54</v>
       </c>
@@ -6145,7 +6146,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>54</v>
       </c>
@@ -6159,7 +6160,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>54</v>
       </c>
@@ -6173,7 +6174,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>54</v>
       </c>
@@ -6187,7 +6188,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>54</v>
       </c>
@@ -6201,7 +6202,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>54</v>
       </c>
@@ -6215,7 +6216,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>54</v>
       </c>
@@ -6229,7 +6230,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>54</v>
       </c>
@@ -6243,7 +6244,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>54</v>
       </c>
@@ -6257,7 +6258,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>54</v>
       </c>
@@ -6271,7 +6272,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>56</v>
       </c>
@@ -6285,7 +6286,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>56</v>
       </c>
@@ -6299,7 +6300,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>56</v>
       </c>
@@ -6313,7 +6314,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>58</v>
       </c>
@@ -6327,7 +6328,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>58</v>
       </c>
@@ -6341,7 +6342,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>58</v>
       </c>
@@ -6355,7 +6356,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>58</v>
       </c>
@@ -6369,7 +6370,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>58</v>
       </c>
@@ -6383,7 +6384,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>58</v>
       </c>
@@ -6397,7 +6398,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>58</v>
       </c>
@@ -6411,7 +6412,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>58</v>
       </c>
@@ -6425,7 +6426,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>60</v>
       </c>
@@ -6439,7 +6440,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>60</v>
       </c>
@@ -6453,7 +6454,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>60</v>
       </c>
@@ -6467,7 +6468,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>62</v>
       </c>
@@ -6481,7 +6482,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>62</v>
       </c>
@@ -6495,7 +6496,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>64</v>
       </c>
@@ -6509,7 +6510,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>64</v>
       </c>
@@ -6523,7 +6524,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>64</v>
       </c>
@@ -6537,7 +6538,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>64</v>
       </c>
@@ -6551,7 +6552,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>64</v>
       </c>
@@ -6565,7 +6566,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>64</v>
       </c>
@@ -6579,7 +6580,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>64</v>
       </c>
@@ -6604,34 +6605,34 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AC73EE4-C981-4A0D-A864-B1E4468C5E73}">
   <dimension ref="A1:AO17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="18" max="18" width="11.88671875" customWidth="1"/>
-    <col min="20" max="20" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.90625" customWidth="1"/>
+    <col min="20" max="20" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="18.08984375" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="12" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.453125" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="12" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.453125" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="13" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.453125" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="13" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>270</v>
       </c>
@@ -6689,74 +6690,74 @@
       <c r="S1" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="T1" s="28" t="s">
+      <c r="T1" s="17" t="s">
         <v>313</v>
       </c>
-      <c r="U1" s="28" t="s">
+      <c r="U1" s="17" t="s">
         <v>314</v>
       </c>
-      <c r="V1" s="28" t="s">
+      <c r="V1" s="17" t="s">
         <v>315</v>
       </c>
-      <c r="W1" s="28" t="s">
+      <c r="W1" s="17" t="s">
         <v>316</v>
       </c>
-      <c r="X1" s="28" t="s">
+      <c r="X1" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="Y1" s="28" t="s">
+      <c r="Y1" s="17" t="s">
         <v>318</v>
       </c>
-      <c r="Z1" s="28" t="s">
+      <c r="Z1" s="17" t="s">
         <v>319</v>
       </c>
-      <c r="AA1" s="28" t="s">
+      <c r="AA1" s="17" t="s">
         <v>320</v>
       </c>
-      <c r="AB1" s="28" t="s">
+      <c r="AB1" s="17" t="s">
         <v>321</v>
       </c>
-      <c r="AC1" s="28" t="s">
+      <c r="AC1" s="17" t="s">
         <v>322</v>
       </c>
-      <c r="AD1" s="28" t="s">
+      <c r="AD1" s="17" t="s">
         <v>323</v>
       </c>
-      <c r="AE1" s="28" t="s">
+      <c r="AE1" s="17" t="s">
         <v>324</v>
       </c>
-      <c r="AF1" s="28" t="s">
+      <c r="AF1" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="AG1" s="28" t="s">
+      <c r="AG1" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="AH1" s="28" t="s">
+      <c r="AH1" s="17" t="s">
         <v>338</v>
       </c>
-      <c r="AI1" s="28" t="s">
+      <c r="AI1" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="AJ1" s="28" t="s">
+      <c r="AJ1" s="17" t="s">
         <v>340</v>
       </c>
-      <c r="AK1" s="28" t="s">
+      <c r="AK1" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="AL1" s="28" t="s">
+      <c r="AL1" s="17" t="s">
         <v>342</v>
       </c>
-      <c r="AM1" s="28" t="s">
+      <c r="AM1" s="17" t="s">
         <v>343</v>
       </c>
-      <c r="AN1" s="28" t="s">
+      <c r="AN1" s="17" t="s">
         <v>344</v>
       </c>
-      <c r="AO1" s="28" t="s">
+      <c r="AO1" s="17" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="2" spans="1:41" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:41" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -6797,13 +6798,13 @@
       </c>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
-      <c r="Q2" s="17" t="s">
+      <c r="Q2" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="R2" s="17" t="s">
+      <c r="R2" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="S2" s="17">
+      <c r="S2" s="4">
         <v>75183508</v>
       </c>
       <c r="T2" s="3">
@@ -6812,68 +6813,68 @@
       <c r="U2" s="3">
         <v>5</v>
       </c>
-      <c r="V2" s="17">
+      <c r="V2" s="4">
         <v>1</v>
       </c>
-      <c r="W2" s="17">
+      <c r="W2" s="4">
         <v>5</v>
       </c>
-      <c r="X2" s="17">
+      <c r="X2" s="4">
         <v>1</v>
       </c>
-      <c r="Y2" s="17">
+      <c r="Y2" s="4">
         <v>5</v>
       </c>
-      <c r="Z2" s="17">
+      <c r="Z2" s="4">
         <v>1</v>
       </c>
-      <c r="AA2" s="17">
+      <c r="AA2" s="4">
         <v>5</v>
       </c>
-      <c r="AB2" s="17">
+      <c r="AB2" s="4">
         <v>1</v>
       </c>
-      <c r="AC2" s="17">
+      <c r="AC2" s="4">
         <v>5</v>
       </c>
-      <c r="AD2" s="17">
+      <c r="AD2" s="4">
         <v>1</v>
       </c>
-      <c r="AE2" s="17">
+      <c r="AE2" s="4">
         <v>5</v>
       </c>
-      <c r="AF2" s="17">
+      <c r="AF2" s="4">
         <v>1</v>
       </c>
-      <c r="AG2" s="17">
+      <c r="AG2" s="4">
         <v>5</v>
       </c>
-      <c r="AH2" s="17">
+      <c r="AH2" s="4">
         <v>1</v>
       </c>
-      <c r="AI2" s="17">
+      <c r="AI2" s="4">
         <v>5</v>
       </c>
-      <c r="AJ2" s="17">
+      <c r="AJ2" s="4">
         <v>1</v>
       </c>
-      <c r="AK2" s="17">
+      <c r="AK2" s="4">
         <v>5</v>
       </c>
-      <c r="AL2" s="17">
+      <c r="AL2" s="4">
         <v>1</v>
       </c>
-      <c r="AM2" s="17">
+      <c r="AM2" s="4">
         <v>5</v>
       </c>
-      <c r="AN2" s="17">
+      <c r="AN2" s="4">
         <v>1</v>
       </c>
-      <c r="AO2" s="17">
+      <c r="AO2" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -6918,41 +6919,41 @@
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="A7" s="32" t="s">
         <v>380</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="F7" s="23" t="s">
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="F7" s="29" t="s">
         <v>311</v>
       </c>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-    </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A8" s="20"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-    </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A9" s="22" t="s">
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+    </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="A8" s="32"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+    </row>
+    <row r="9" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="A9" s="33" t="s">
         <v>292</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="21"/>
-    </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E17" s="21"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="13"/>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E17" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -6970,15 +6971,15 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293D15E-4FC9-4B7D-8BBA-907695DFF0A6}">
   <dimension ref="A1:L24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="51.5546875" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.54296875" customWidth="1"/>
+    <col min="4" max="4" width="13.36328125" customWidth="1"/>
+    <col min="6" max="6" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>270</v>
       </c>
@@ -7000,18 +7001,18 @@
       <c r="G1" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="12" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="19" t="s">
         <v>271</v>
       </c>
       <c r="D2" s="3">
@@ -7028,14 +7029,14 @@
         <v>334</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="28.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="19" t="s">
         <v>272</v>
       </c>
       <c r="D3" s="3">
@@ -7052,14 +7053,14 @@
         <v>334</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="19" t="s">
         <v>298</v>
       </c>
       <c r="D4" s="3">
@@ -7075,20 +7076,20 @@
       <c r="H4" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="J4" s="19" t="s">
+      <c r="J4" s="34" t="s">
         <v>353</v>
       </c>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-    </row>
-    <row r="5" spans="1:12" ht="116.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+    </row>
+    <row r="5" spans="1:12" ht="116.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="19" t="s">
         <v>273</v>
       </c>
       <c r="D5" s="3">
@@ -7104,18 +7105,18 @@
       <c r="H5" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-    </row>
-    <row r="6" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34"/>
+    </row>
+    <row r="6" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="19" t="s">
         <v>274</v>
       </c>
       <c r="D6" s="3">
@@ -7132,14 +7133,14 @@
         <v>334</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="19" t="s">
         <v>291</v>
       </c>
       <c r="D7" s="3">
@@ -7156,14 +7157,14 @@
         <v>334</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="C8" s="32"/>
+      <c r="C8" s="19"/>
       <c r="D8" s="3">
         <v>0</v>
       </c>
@@ -7178,14 +7179,14 @@
         <v>334</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>1</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="32"/>
+      <c r="C9" s="19"/>
       <c r="D9" s="3">
         <v>0</v>
       </c>
@@ -7200,14 +7201,14 @@
         <v>334</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>1</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="19" t="s">
         <v>286</v>
       </c>
       <c r="D10" s="3">
@@ -7224,14 +7225,14 @@
         <v>334</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="43.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>1</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="20" t="s">
         <v>329</v>
       </c>
       <c r="D11" s="3">
@@ -7248,14 +7249,14 @@
         <v>334</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>1</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="20" t="s">
         <v>329</v>
       </c>
       <c r="D12" s="3">
@@ -7271,16 +7272,15 @@
       <c r="H12" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="I12" s="27"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>1</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="20" t="s">
         <v>329</v>
       </c>
       <c r="D13" s="3">
@@ -7296,16 +7296,15 @@
       <c r="H13" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="I13" s="27"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>1</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="20" t="s">
         <v>329</v>
       </c>
       <c r="D14" s="3">
@@ -7321,16 +7320,15 @@
       <c r="H14" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="I14" s="27"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>1</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="20" t="s">
         <v>329</v>
       </c>
       <c r="D15" s="3">
@@ -7346,16 +7344,15 @@
       <c r="H15" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="I15" s="27"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>1</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="20" t="s">
         <v>329</v>
       </c>
       <c r="D16" s="3">
@@ -7371,141 +7368,135 @@
       <c r="H16" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="I16" s="27"/>
-    </row>
-    <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>1</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="15" t="s">
         <v>310</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" s="21" t="s">
         <v>329</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="15">
         <v>1</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="15">
         <v>5</v>
       </c>
-      <c r="F17" s="25" t="s">
+      <c r="F17" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="G17" s="25"/>
+      <c r="G17" s="15"/>
       <c r="H17" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="I17" s="27"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>1</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" s="21" t="s">
         <v>329</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="15">
         <v>1</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="15">
         <v>5</v>
       </c>
-      <c r="F18" s="25" t="s">
+      <c r="F18" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="G18" s="25"/>
+      <c r="G18" s="15"/>
       <c r="H18" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="I18" s="27"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>1</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="16" t="s">
         <v>326</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" s="21" t="s">
         <v>329</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="15">
         <v>1</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="15">
         <v>5</v>
       </c>
-      <c r="F19" s="25" t="s">
+      <c r="F19" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="G19" s="25"/>
+      <c r="G19" s="15"/>
       <c r="H19" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="I19" s="27"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>1</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="16" t="s">
         <v>327</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" s="21" t="s">
         <v>329</v>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="15">
         <v>1</v>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="15">
         <v>5</v>
       </c>
-      <c r="F20" s="25" t="s">
+      <c r="F20" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="G20" s="25"/>
+      <c r="G20" s="15"/>
       <c r="H20" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="I20" s="27"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>1</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="16" t="s">
         <v>328</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" s="21" t="s">
         <v>329</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="15">
         <v>1</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="15">
         <v>5</v>
       </c>
-      <c r="F21" s="25" t="s">
+      <c r="F21" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="G21" s="25"/>
+      <c r="G21" s="15"/>
       <c r="H21" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="I21" s="27"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="18">
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="3">
         <v>1</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="C22" s="35" t="s">
+      <c r="C22" s="19" t="s">
         <v>331</v>
       </c>
       <c r="D22" s="3"/>
@@ -7516,14 +7507,14 @@
         <v>335</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="18">
+    <row r="23" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="3">
         <v>1</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="C23" s="35" t="s">
+      <c r="C23" s="19" t="s">
         <v>332</v>
       </c>
       <c r="D23" s="3"/>
@@ -7534,14 +7525,14 @@
         <v>335</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="18">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="3">
         <v>1</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="C24" s="36" t="s">
+      <c r="C24" s="20" t="s">
         <v>333</v>
       </c>
       <c r="D24" s="3"/>
